--- a/系统开发字段说明.xlsx
+++ b/系统开发字段说明.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kongf\Desktop\集运系统\JIYUN-ADMIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE9D1CD-5C70-4E42-85DB-7A264A599A5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CAED51F-8DE9-4814-9B91-D237085E77F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37680" yWindow="3285" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="包裹状态字典" sheetId="1" r:id="rId1"/>
     <sheet name="库位管理" sheetId="3" r:id="rId2"/>
+    <sheet name="代购订单管理" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="179">
   <si>
     <t>字段：</t>
   </si>
@@ -2933,4 +2934,658 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67522C72-12D8-48E2-AD4C-816A16959AA6}">
+  <dimension ref="A1:S58"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="11.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="32.58203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.9140625" customWidth="1"/>
+    <col min="5" max="8" width="10.9140625" style="2" customWidth="1"/>
+    <col min="9" max="11" width="10.75" style="2" customWidth="1"/>
+    <col min="12" max="13" width="9.83203125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="14" style="2" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="12.4140625" style="2" customWidth="1"/>
+    <col min="17" max="18" width="18.1640625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="28.08203125" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="12.33203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" s="11" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" s="13" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="L3" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="S3" s="13" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15"/>
+      <c r="P8" s="2"/>
+    </row>
+    <row r="9" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15"/>
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15"/>
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15"/>
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="15"/>
+      <c r="P12" s="2"/>
+    </row>
+    <row r="13" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="15"/>
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="15"/>
+      <c r="P24" s="2"/>
+    </row>
+    <row r="25" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="15"/>
+      <c r="P25" s="2"/>
+    </row>
+    <row r="26" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="15"/>
+      <c r="P26" s="2"/>
+    </row>
+    <row r="27" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="15"/>
+      <c r="P27" s="2"/>
+    </row>
+    <row r="28" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="15"/>
+      <c r="C28" s="12"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="P28" s="2"/>
+    </row>
+    <row r="29" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="15"/>
+      <c r="C29" s="12"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="P29" s="2"/>
+    </row>
+    <row r="30" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="15"/>
+      <c r="C30" s="12"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="P30" s="2"/>
+    </row>
+    <row r="31" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="15"/>
+      <c r="C31" s="12"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="P31" s="2"/>
+    </row>
+    <row r="32" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="15"/>
+      <c r="C32" s="12"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="P32" s="2"/>
+    </row>
+    <row r="33" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="15"/>
+      <c r="C33" s="12"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="P33" s="2"/>
+    </row>
+    <row r="34" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="15"/>
+      <c r="C34" s="12"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="P34" s="2"/>
+    </row>
+    <row r="35" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="15"/>
+      <c r="C35" s="12"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="P35" s="2"/>
+    </row>
+    <row r="36" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="15"/>
+      <c r="C36" s="12"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="P36" s="2"/>
+    </row>
+    <row r="37" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="15"/>
+      <c r="C37" s="12"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="P37" s="2"/>
+    </row>
+    <row r="38" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="15"/>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="15"/>
+      <c r="P39" s="2"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C40" s="5"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C41" s="5"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C42" s="5"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C43" s="5"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C44" s="5"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C45" s="5"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C46" s="5"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C47" s="10"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C48" s="10"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C49" s="10"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C50" s="5"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C51" s="5"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C52" s="5"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C53" s="5"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D54" s="2"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D55" s="2"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D56" s="2"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D57" s="2"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D58" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D3:H3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/系统开发字段说明.xlsx
+++ b/系统开发字段说明.xlsx
@@ -8,14 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kongf\Desktop\集运系统\JIYUN-ADMIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CAED51F-8DE9-4814-9B91-D237085E77F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC8F5A2-1C0D-42BD-A1F0-08950929A8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16420" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="包裹状态字典" sheetId="1" r:id="rId1"/>
     <sheet name="库位管理" sheetId="3" r:id="rId2"/>
     <sheet name="代购订单管理" sheetId="4" r:id="rId3"/>
+    <sheet name="渠道管理" sheetId="5" r:id="rId4"/>
+    <sheet name="标签管理" sheetId="6" r:id="rId5"/>
+    <sheet name="单号库" sheetId="7" r:id="rId6"/>
+    <sheet name="运单管理" sheetId="8" r:id="rId7"/>
+    <sheet name="地址簿" sheetId="9" r:id="rId8"/>
+    <sheet name="XXXXXXX" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="227">
   <si>
     <t>字段：</t>
   </si>
@@ -601,6 +607,200 @@
   <si>
     <t>是/否
 默认“是”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>渠道名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>标签名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>label_name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.物流商账号添加的时候，自动绑定物流商；
+2.平台账号，选填；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>template_html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HTML模板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>唯一</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要上传模板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>号段名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是/否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>库存数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“未使用”的单号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>number_category</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“未使用”/“已用”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>number</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必须关联
+&lt;号段名称&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每24个小时，做一次判断（根据近期使用状况）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预计用尽天数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>运单号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>渠道批次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>件数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代收款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>缴税方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体积</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>货物态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>信息态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可留空，或者选择：发件人/承运商/收件人/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据长宽高自动计算生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物品清单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>货物图片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0-多张</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>会员</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发件人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>收件人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-多个物品名称，包含字段：&lt;*物品名称&gt;&lt;物品类别&gt;&lt;*价值&gt;&lt;*件数&gt;，带*号必填</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>字段名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姓名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地址</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>区域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必填，根据选择的区域配上国际电话代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必选，可以选择中国大陆、台湾、香港、澳门的区域</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -608,7 +808,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -657,6 +857,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -678,7 +885,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -723,7 +930,16 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2431,13 +2647,13 @@
       <c r="C3" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
       <c r="I3" s="13" t="s">
         <v>173</v>
       </c>
@@ -3023,7 +3239,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>151</v>
@@ -3581,9 +3797,2352 @@
       <c r="D58" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="D3:H3"/>
-  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBFDA69-2E4B-4796-8839-B70CBD0249B0}">
+  <dimension ref="A1:S58"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="11.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.9140625" customWidth="1"/>
+    <col min="5" max="8" width="10.9140625" style="2" customWidth="1"/>
+    <col min="9" max="11" width="10.75" style="2" customWidth="1"/>
+    <col min="12" max="13" width="9.83203125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="14" style="2" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="12.4140625" style="2" customWidth="1"/>
+    <col min="17" max="18" width="18.1640625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="28.08203125" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="12.33203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" s="11" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" s="13" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15"/>
+      <c r="P8" s="2"/>
+    </row>
+    <row r="9" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15"/>
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15"/>
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15"/>
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="15"/>
+      <c r="P12" s="2"/>
+    </row>
+    <row r="13" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="15"/>
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="15"/>
+      <c r="P24" s="2"/>
+    </row>
+    <row r="25" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="15"/>
+      <c r="P25" s="2"/>
+    </row>
+    <row r="26" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="15"/>
+      <c r="P26" s="2"/>
+    </row>
+    <row r="27" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="15"/>
+      <c r="P27" s="2"/>
+    </row>
+    <row r="28" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="15"/>
+      <c r="C28" s="12"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="P28" s="2"/>
+    </row>
+    <row r="29" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="15"/>
+      <c r="C29" s="12"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="P29" s="2"/>
+    </row>
+    <row r="30" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="15"/>
+      <c r="C30" s="12"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="P30" s="2"/>
+    </row>
+    <row r="31" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="15"/>
+      <c r="C31" s="12"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="P31" s="2"/>
+    </row>
+    <row r="32" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="15"/>
+      <c r="C32" s="12"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="P32" s="2"/>
+    </row>
+    <row r="33" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="15"/>
+      <c r="C33" s="12"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="P33" s="2"/>
+    </row>
+    <row r="34" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="15"/>
+      <c r="C34" s="12"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="P34" s="2"/>
+    </row>
+    <row r="35" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="15"/>
+      <c r="C35" s="12"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="P35" s="2"/>
+    </row>
+    <row r="36" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="15"/>
+      <c r="C36" s="12"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="P36" s="2"/>
+    </row>
+    <row r="37" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="15"/>
+      <c r="C37" s="12"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="P37" s="2"/>
+    </row>
+    <row r="38" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="15"/>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="15"/>
+      <c r="P39" s="2"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C40" s="5"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C41" s="5"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C42" s="5"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C43" s="5"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C44" s="5"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C45" s="5"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C46" s="5"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C47" s="10"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C48" s="10"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C49" s="10"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C50" s="5"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C51" s="5"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C52" s="5"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C53" s="5"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D54" s="2"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D55" s="2"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D56" s="2"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D57" s="2"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D58" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1450033-3EA4-4DCC-A4C1-0125BDFFFB69}">
+  <dimension ref="A1:I55"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="11.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.4140625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="18.1640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="41.4140625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="12.33203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="11" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="13" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="15"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="15"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="24" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="15"/>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="15"/>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="15"/>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="15"/>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="15"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="2"/>
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="15"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="2"/>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="15"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="2"/>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="15"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="2"/>
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="15"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="2"/>
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="15"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="2"/>
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="15"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="2"/>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="15"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="2"/>
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="15"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="2"/>
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="15"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="2"/>
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="15"/>
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="15"/>
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+    </row>
+    <row r="49" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
+    </row>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+    </row>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+    </row>
+    <row r="52" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+    </row>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+    </row>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D55" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89607AB6-44F6-4EFC-A6F5-AF2165424DFB}">
+  <dimension ref="A1:O53"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="11.75" style="2" customWidth="1"/>
+    <col min="3" max="5" width="19.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.4140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="18.1640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="28.08203125" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="12.33203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="11" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="13" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" s="11" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="13" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O19" s="13"/>
+    </row>
+    <row r="24" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="15"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="15"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="15"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="15"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="15"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="15"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="15"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="15"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="15"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="15"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="G33" s="2"/>
+    </row>
+    <row r="34" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="15"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="15"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="15"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="15"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="15"/>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="15"/>
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+    </row>
+    <row r="49" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10"/>
+    </row>
+    <row r="50" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+    </row>
+    <row r="51" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+    </row>
+    <row r="52" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+    </row>
+    <row r="53" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33906C0D-BD2E-46FD-BACB-143C3F60348C}">
+  <dimension ref="A1:N56"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="11.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="85.6640625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="10.9140625" style="4" customWidth="1"/>
+    <col min="5" max="8" width="10.9140625" style="5" customWidth="1"/>
+    <col min="9" max="11" width="10.75" style="5" customWidth="1"/>
+    <col min="12" max="13" width="9.83203125" style="5" customWidth="1"/>
+    <col min="14" max="14" width="14" style="5" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" style="5" customWidth="1"/>
+    <col min="16" max="16" width="12.4140625" style="5" customWidth="1"/>
+    <col min="17" max="18" width="18.1640625" style="5" customWidth="1"/>
+    <col min="19" max="19" width="28.08203125" style="5" customWidth="1"/>
+    <col min="20" max="16384" width="12.33203125" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="5"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D23" s="5"/>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B26" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D26" s="5"/>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B27" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D29" s="5"/>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D30" s="5"/>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D31" s="5"/>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D32" s="5"/>
+    </row>
+    <row r="33" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D33" s="5"/>
+    </row>
+    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D34" s="5"/>
+    </row>
+    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D35" s="5"/>
+    </row>
+    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D36" s="5"/>
+    </row>
+    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D37" s="5"/>
+    </row>
+    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D38" s="5"/>
+    </row>
+    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D39" s="5"/>
+    </row>
+    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D40" s="5"/>
+    </row>
+    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D41" s="5"/>
+    </row>
+    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D42" s="5"/>
+    </row>
+    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D43" s="5"/>
+    </row>
+    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D44" s="5"/>
+    </row>
+    <row r="45" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C45" s="19"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+    </row>
+    <row r="46" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C46" s="19"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+    </row>
+    <row r="47" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C47" s="19"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+    </row>
+    <row r="48" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D48" s="5"/>
+    </row>
+    <row r="49" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D49" s="5"/>
+    </row>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D50" s="5"/>
+    </row>
+    <row r="51" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D51" s="5"/>
+    </row>
+    <row r="52" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D52" s="5"/>
+    </row>
+    <row r="53" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D53" s="5"/>
+    </row>
+    <row r="54" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D54" s="5"/>
+    </row>
+    <row r="55" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D55" s="5"/>
+    </row>
+    <row r="56" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D56" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44ADB29C-CB17-420C-8D8F-0227DF69DE78}">
+  <dimension ref="A1:P16"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="11.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="85.6640625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="10.9140625" customWidth="1"/>
+    <col min="5" max="8" width="10.9140625" style="2" customWidth="1"/>
+    <col min="9" max="11" width="10.75" style="2" customWidth="1"/>
+    <col min="12" max="13" width="9.83203125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="14" style="2" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="12.4140625" style="2" customWidth="1"/>
+    <col min="17" max="18" width="18.1640625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="28.08203125" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="12.33203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="P5" s="2"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C9" s="20"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C10" s="20"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D11" s="2"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D13" s="2"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D16" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50E289C6-4857-403B-BCF4-4E6CA413AF65}">
+  <dimension ref="A1:S58"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="11.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.9140625" customWidth="1"/>
+    <col min="5" max="8" width="10.9140625" style="2" customWidth="1"/>
+    <col min="9" max="11" width="10.75" style="2" customWidth="1"/>
+    <col min="12" max="13" width="9.83203125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="14" style="2" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="12.4140625" style="2" customWidth="1"/>
+    <col min="17" max="18" width="18.1640625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="28.08203125" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="12.33203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" s="11" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" s="13" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15"/>
+      <c r="P8" s="2"/>
+    </row>
+    <row r="9" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15"/>
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15"/>
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15"/>
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="15"/>
+      <c r="P12" s="2"/>
+    </row>
+    <row r="13" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="15"/>
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="15"/>
+      <c r="P24" s="2"/>
+    </row>
+    <row r="25" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="15"/>
+      <c r="P25" s="2"/>
+    </row>
+    <row r="26" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="15"/>
+      <c r="P26" s="2"/>
+    </row>
+    <row r="27" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="15"/>
+      <c r="P27" s="2"/>
+    </row>
+    <row r="28" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="15"/>
+      <c r="C28" s="12"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="P28" s="2"/>
+    </row>
+    <row r="29" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="15"/>
+      <c r="C29" s="12"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="P29" s="2"/>
+    </row>
+    <row r="30" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="15"/>
+      <c r="C30" s="12"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="P30" s="2"/>
+    </row>
+    <row r="31" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="15"/>
+      <c r="C31" s="12"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="P31" s="2"/>
+    </row>
+    <row r="32" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="15"/>
+      <c r="C32" s="12"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="P32" s="2"/>
+    </row>
+    <row r="33" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="15"/>
+      <c r="C33" s="12"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="P33" s="2"/>
+    </row>
+    <row r="34" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="15"/>
+      <c r="C34" s="12"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="P34" s="2"/>
+    </row>
+    <row r="35" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="15"/>
+      <c r="C35" s="12"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="P35" s="2"/>
+    </row>
+    <row r="36" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="15"/>
+      <c r="C36" s="12"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="P36" s="2"/>
+    </row>
+    <row r="37" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="15"/>
+      <c r="C37" s="12"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="P37" s="2"/>
+    </row>
+    <row r="38" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="15"/>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="15"/>
+      <c r="P39" s="2"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C40" s="5"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C41" s="5"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C42" s="5"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C43" s="5"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C44" s="5"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C45" s="5"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C46" s="5"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C47" s="10"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C48" s="10"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C49" s="10"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C50" s="5"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C51" s="5"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C52" s="5"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C53" s="5"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D54" s="2"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D55" s="2"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D56" s="2"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D57" s="2"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D58" s="2"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>

--- a/系统开发字段说明.xlsx
+++ b/系统开发字段说明.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kongf\Desktop\集运系统\JIYUN-ADMIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC8F5A2-1C0D-42BD-A1F0-08950929A8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4652BC77-AB62-4588-AD11-7046CFA1EE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16420" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37680" yWindow="3285" windowWidth="38640" windowHeight="21240" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="包裹状态字典" sheetId="1" r:id="rId1"/>
     <sheet name="库位管理" sheetId="3" r:id="rId2"/>
-    <sheet name="代购订单管理" sheetId="4" r:id="rId3"/>
-    <sheet name="渠道管理" sheetId="5" r:id="rId4"/>
-    <sheet name="标签管理" sheetId="6" r:id="rId5"/>
-    <sheet name="单号库" sheetId="7" r:id="rId6"/>
-    <sheet name="运单管理" sheetId="8" r:id="rId7"/>
-    <sheet name="地址簿" sheetId="9" r:id="rId8"/>
-    <sheet name="XXXXXXX" sheetId="10" r:id="rId9"/>
+    <sheet name="标签管理" sheetId="6" r:id="rId3"/>
+    <sheet name="单号库" sheetId="7" r:id="rId4"/>
+    <sheet name="地址簿" sheetId="9" r:id="rId5"/>
+    <sheet name="航线运输管理" sheetId="11" r:id="rId6"/>
+    <sheet name="渠道管理" sheetId="5" r:id="rId7"/>
+    <sheet name="第三方派送" sheetId="10" r:id="rId8"/>
+    <sheet name="运单管理" sheetId="8" r:id="rId9"/>
+    <sheet name="代购订单管理" sheetId="4" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="285">
   <si>
     <t>字段：</t>
   </si>
@@ -801,6 +802,225 @@
   </si>
   <si>
     <t>必选，可以选择中国大陆、台湾、香港、澳门的区域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从地址簿中选择，同时可以CRUD地址簿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>模仿包裹的逻辑，必须从包裹状态字典中选取</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>渠道名称</t>
+  </si>
+  <si>
+    <t>&lt;运单号&gt;+&lt;物流商&gt;，复核唯一</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>logistics_provider_id</t>
+  </si>
+  <si>
+    <t>物流商</t>
+  </si>
+  <si>
+    <t>包裹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选填，关联多个包裹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>航线字段：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>航线名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>承运人</t>
+  </si>
+  <si>
+    <t>航线代码</t>
+  </si>
+  <si>
+    <t>必填</t>
+  </si>
+  <si>
+    <t>必选：是/否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预计启航时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预计到港时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实际启航时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实际到港时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>截单时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>截VGM时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集装箱字段：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箱号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箱型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必选</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提单号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发货人</t>
+  </si>
+  <si>
+    <t>收货人</t>
+  </si>
+  <si>
+    <t>通知人</t>
+  </si>
+  <si>
+    <t>班(航)次号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>唯一，必填</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交货截止时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>起运港</t>
+  </si>
+  <si>
+    <t>目的港</t>
+  </si>
+  <si>
+    <t>班(航)名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交货地</t>
+  </si>
+  <si>
+    <t>起运港</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必填，默认为关系班(航)的&lt;起运港&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集装箱号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>封条号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>唛头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>承运类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必选：“海运”/“空运”/“陆运”/“铁路”/“水运”/“其它”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>承运工具名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以自行定义，或者从集装箱列表中选择启用的集装箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>唯一，选填</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>班(航)次名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>班(航)次字段：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>货物状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提(运)单管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>字段：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>班(航)次管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>航线管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集装箱管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用包裹状态字典的货物态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多个港口用“/”分开</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多个港口用“/”分开，默认为</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必填，默认为关系班(航)的&lt;目的港&gt;；如果关联的&lt;班(航)次&gt;的&lt;目的港&gt;为：aa/bb则需要选择“aa”/“bb”；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -808,7 +1028,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -864,16 +1084,58 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -881,11 +1143,146 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -932,14 +1329,107 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2499,6 +2989,657 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67522C72-12D8-48E2-AD4C-816A16959AA6}">
+  <dimension ref="A1:S58"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="11.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="32.58203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.9140625" customWidth="1"/>
+    <col min="5" max="8" width="10.9140625" style="2" customWidth="1"/>
+    <col min="9" max="11" width="10.75" style="2" customWidth="1"/>
+    <col min="12" max="13" width="9.83203125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="14" style="2" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="12.4140625" style="2" customWidth="1"/>
+    <col min="17" max="18" width="18.1640625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="28.08203125" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="12.33203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" s="11" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" s="13" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="L3" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="S3" s="13" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15"/>
+      <c r="P8" s="2"/>
+    </row>
+    <row r="9" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15"/>
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15"/>
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15"/>
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="15"/>
+      <c r="P12" s="2"/>
+    </row>
+    <row r="13" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="15"/>
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="15"/>
+      <c r="P24" s="2"/>
+    </row>
+    <row r="25" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="15"/>
+      <c r="P25" s="2"/>
+    </row>
+    <row r="26" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="15"/>
+      <c r="P26" s="2"/>
+    </row>
+    <row r="27" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="15"/>
+      <c r="P27" s="2"/>
+    </row>
+    <row r="28" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="15"/>
+      <c r="C28" s="12"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="P28" s="2"/>
+    </row>
+    <row r="29" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="15"/>
+      <c r="C29" s="12"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="P29" s="2"/>
+    </row>
+    <row r="30" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="15"/>
+      <c r="C30" s="12"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="P30" s="2"/>
+    </row>
+    <row r="31" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="15"/>
+      <c r="C31" s="12"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="P31" s="2"/>
+    </row>
+    <row r="32" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="15"/>
+      <c r="C32" s="12"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="P32" s="2"/>
+    </row>
+    <row r="33" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="15"/>
+      <c r="C33" s="12"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="P33" s="2"/>
+    </row>
+    <row r="34" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="15"/>
+      <c r="C34" s="12"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="P34" s="2"/>
+    </row>
+    <row r="35" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="15"/>
+      <c r="C35" s="12"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="P35" s="2"/>
+    </row>
+    <row r="36" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="15"/>
+      <c r="C36" s="12"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="P36" s="2"/>
+    </row>
+    <row r="37" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="15"/>
+      <c r="C37" s="12"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="P37" s="2"/>
+    </row>
+    <row r="38" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="15"/>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="15"/>
+      <c r="P39" s="2"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C40" s="5"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C41" s="5"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C42" s="5"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C43" s="5"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C44" s="5"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C45" s="5"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C46" s="5"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C47" s="10"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C48" s="10"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C49" s="10"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C50" s="5"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C51" s="5"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C52" s="5"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C53" s="5"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D54" s="2"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D55" s="2"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D56" s="2"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D57" s="2"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D58" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2122232B-336C-48B5-9283-6A91D40EFFD9}">
   <dimension ref="A1:S58"/>
@@ -2647,13 +3788,13 @@
       <c r="C3" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
       <c r="I3" s="13" t="s">
         <v>173</v>
       </c>
@@ -3153,1276 +4294,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67522C72-12D8-48E2-AD4C-816A16959AA6}">
-  <dimension ref="A1:S58"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.33203125" style="15" customWidth="1"/>
-    <col min="2" max="2" width="11.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="32.58203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.9140625" customWidth="1"/>
-    <col min="5" max="8" width="10.9140625" style="2" customWidth="1"/>
-    <col min="9" max="11" width="10.75" style="2" customWidth="1"/>
-    <col min="12" max="13" width="9.83203125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="14" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="12.4140625" style="2" customWidth="1"/>
-    <col min="17" max="18" width="18.1640625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="28.08203125" style="2" customWidth="1"/>
-    <col min="20" max="16384" width="12.33203125" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" s="11" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="M1" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="O1" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q1" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="R1" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="S1" s="11" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" s="13" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="L3" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="M3" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="N3" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="O3" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="P3" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="S3" s="13" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15"/>
-      <c r="P8" s="2"/>
-    </row>
-    <row r="9" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15"/>
-      <c r="P9" s="2"/>
-    </row>
-    <row r="10" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15"/>
-      <c r="P10" s="2"/>
-    </row>
-    <row r="11" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15"/>
-      <c r="P11" s="2"/>
-    </row>
-    <row r="12" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15"/>
-      <c r="P12" s="2"/>
-    </row>
-    <row r="13" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="15"/>
-      <c r="P13" s="2"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D23" s="2"/>
-    </row>
-    <row r="24" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="15"/>
-      <c r="P24" s="2"/>
-    </row>
-    <row r="25" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="15"/>
-      <c r="P25" s="2"/>
-    </row>
-    <row r="26" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="15"/>
-      <c r="P26" s="2"/>
-    </row>
-    <row r="27" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="15"/>
-      <c r="P27" s="2"/>
-    </row>
-    <row r="28" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="15"/>
-      <c r="C28" s="12"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
-      <c r="P28" s="2"/>
-    </row>
-    <row r="29" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="15"/>
-      <c r="C29" s="12"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
-      <c r="P29" s="2"/>
-    </row>
-    <row r="30" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="15"/>
-      <c r="C30" s="12"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
-      <c r="P30" s="2"/>
-    </row>
-    <row r="31" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="15"/>
-      <c r="C31" s="12"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
-      <c r="P31" s="2"/>
-    </row>
-    <row r="32" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="15"/>
-      <c r="C32" s="12"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
-      <c r="P32" s="2"/>
-    </row>
-    <row r="33" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="15"/>
-      <c r="C33" s="12"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
-      <c r="P33" s="2"/>
-    </row>
-    <row r="34" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="15"/>
-      <c r="C34" s="12"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-      <c r="N34" s="2"/>
-      <c r="P34" s="2"/>
-    </row>
-    <row r="35" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="15"/>
-      <c r="C35" s="12"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-      <c r="N35" s="2"/>
-      <c r="P35" s="2"/>
-    </row>
-    <row r="36" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="15"/>
-      <c r="C36" s="12"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
-      <c r="P36" s="2"/>
-    </row>
-    <row r="37" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="15"/>
-      <c r="C37" s="12"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2"/>
-      <c r="P37" s="2"/>
-    </row>
-    <row r="38" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="15"/>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="15"/>
-      <c r="P39" s="2"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C40" s="5"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C41" s="5"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C42" s="5"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C43" s="5"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="5"/>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C44" s="5"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C45" s="5"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="5"/>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C46" s="5"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C47" s="10"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
-      <c r="N47" s="10"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C48" s="10"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
-      <c r="N48" s="10"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C49" s="10"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="10"/>
-      <c r="M49" s="10"/>
-      <c r="N49" s="10"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C50" s="5"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="5"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C51" s="5"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C52" s="5"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="5"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="5"/>
-      <c r="M52" s="5"/>
-      <c r="N52" s="5"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C53" s="5"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="5"/>
-      <c r="K53" s="5"/>
-      <c r="L53" s="5"/>
-      <c r="M53" s="5"/>
-      <c r="N53" s="5"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D54" s="2"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D55" s="2"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="5"/>
-      <c r="J55" s="5"/>
-      <c r="K55" s="5"/>
-      <c r="L55" s="5"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="5"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D56" s="2"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D57" s="2"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D58" s="2"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBFDA69-2E4B-4796-8839-B70CBD0249B0}">
-  <dimension ref="A1:S58"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.33203125" style="15" customWidth="1"/>
-    <col min="2" max="2" width="11.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.9140625" customWidth="1"/>
-    <col min="5" max="8" width="10.9140625" style="2" customWidth="1"/>
-    <col min="9" max="11" width="10.75" style="2" customWidth="1"/>
-    <col min="12" max="13" width="9.83203125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="14" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="12.4140625" style="2" customWidth="1"/>
-    <col min="17" max="18" width="18.1640625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="28.08203125" style="2" customWidth="1"/>
-    <col min="20" max="16384" width="12.33203125" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" s="11" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="M1" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="O1" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q1" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="R1" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="S1" s="11" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" s="13" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15"/>
-      <c r="P8" s="2"/>
-    </row>
-    <row r="9" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15"/>
-      <c r="P9" s="2"/>
-    </row>
-    <row r="10" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15"/>
-      <c r="P10" s="2"/>
-    </row>
-    <row r="11" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15"/>
-      <c r="P11" s="2"/>
-    </row>
-    <row r="12" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15"/>
-      <c r="P12" s="2"/>
-    </row>
-    <row r="13" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="15"/>
-      <c r="P13" s="2"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D23" s="2"/>
-    </row>
-    <row r="24" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="15"/>
-      <c r="P24" s="2"/>
-    </row>
-    <row r="25" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="15"/>
-      <c r="P25" s="2"/>
-    </row>
-    <row r="26" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="15"/>
-      <c r="P26" s="2"/>
-    </row>
-    <row r="27" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="15"/>
-      <c r="P27" s="2"/>
-    </row>
-    <row r="28" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="15"/>
-      <c r="C28" s="12"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
-      <c r="P28" s="2"/>
-    </row>
-    <row r="29" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="15"/>
-      <c r="C29" s="12"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
-      <c r="P29" s="2"/>
-    </row>
-    <row r="30" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="15"/>
-      <c r="C30" s="12"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
-      <c r="P30" s="2"/>
-    </row>
-    <row r="31" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="15"/>
-      <c r="C31" s="12"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
-      <c r="P31" s="2"/>
-    </row>
-    <row r="32" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="15"/>
-      <c r="C32" s="12"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
-      <c r="P32" s="2"/>
-    </row>
-    <row r="33" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="15"/>
-      <c r="C33" s="12"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
-      <c r="P33" s="2"/>
-    </row>
-    <row r="34" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="15"/>
-      <c r="C34" s="12"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-      <c r="N34" s="2"/>
-      <c r="P34" s="2"/>
-    </row>
-    <row r="35" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="15"/>
-      <c r="C35" s="12"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-      <c r="N35" s="2"/>
-      <c r="P35" s="2"/>
-    </row>
-    <row r="36" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="15"/>
-      <c r="C36" s="12"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
-      <c r="P36" s="2"/>
-    </row>
-    <row r="37" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="15"/>
-      <c r="C37" s="12"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2"/>
-      <c r="P37" s="2"/>
-    </row>
-    <row r="38" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="15"/>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="15"/>
-      <c r="P39" s="2"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C40" s="5"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C41" s="5"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C42" s="5"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C43" s="5"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="5"/>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C44" s="5"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C45" s="5"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="5"/>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C46" s="5"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C47" s="10"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
-      <c r="N47" s="10"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C48" s="10"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
-      <c r="N48" s="10"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C49" s="10"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="10"/>
-      <c r="M49" s="10"/>
-      <c r="N49" s="10"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C50" s="5"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="5"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C51" s="5"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C52" s="5"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="5"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="5"/>
-      <c r="M52" s="5"/>
-      <c r="N52" s="5"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C53" s="5"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="5"/>
-      <c r="K53" s="5"/>
-      <c r="L53" s="5"/>
-      <c r="M53" s="5"/>
-      <c r="N53" s="5"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D54" s="2"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D55" s="2"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="5"/>
-      <c r="J55" s="5"/>
-      <c r="K55" s="5"/>
-      <c r="L55" s="5"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="5"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D56" s="2"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D57" s="2"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D58" s="2"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1450033-3EA4-4DCC-A4C1-0125BDFFFB69}">
   <dimension ref="A1:I55"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -4687,7 +4558,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89607AB6-44F6-4EFC-A6F5-AF2165424DFB}">
   <dimension ref="A1:O53"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -5012,325 +4883,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33906C0D-BD2E-46FD-BACB-143C3F60348C}">
-  <dimension ref="A1:N56"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.33203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="11.75" style="3" customWidth="1"/>
-    <col min="3" max="3" width="85.6640625" style="12" customWidth="1"/>
-    <col min="4" max="4" width="10.9140625" style="4" customWidth="1"/>
-    <col min="5" max="8" width="10.9140625" style="5" customWidth="1"/>
-    <col min="9" max="11" width="10.75" style="5" customWidth="1"/>
-    <col min="12" max="13" width="9.83203125" style="5" customWidth="1"/>
-    <col min="14" max="14" width="14" style="5" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" style="5" customWidth="1"/>
-    <col min="16" max="16" width="12.4140625" style="5" customWidth="1"/>
-    <col min="17" max="18" width="18.1640625" style="5" customWidth="1"/>
-    <col min="19" max="19" width="28.08203125" style="5" customWidth="1"/>
-    <col min="20" max="16384" width="12.33203125" style="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="5"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="5"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="D3" s="5"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B11" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B13" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B15" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B16" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D17" s="5"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D18" s="5"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B19" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="D19" s="5"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B20" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B21" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D21" s="5"/>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B22" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D22" s="5"/>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D23" s="5"/>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B24" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D24" s="5"/>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D25" s="5"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B26" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D26" s="5"/>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B27" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D27" s="5"/>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D28" s="5"/>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D29" s="5"/>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D30" s="5"/>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D31" s="5"/>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D32" s="5"/>
-    </row>
-    <row r="33" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D33" s="5"/>
-    </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D34" s="5"/>
-    </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D35" s="5"/>
-    </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D36" s="5"/>
-    </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D37" s="5"/>
-    </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D38" s="5"/>
-    </row>
-    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D39" s="5"/>
-    </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D40" s="5"/>
-    </row>
-    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D41" s="5"/>
-    </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D42" s="5"/>
-    </row>
-    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D43" s="5"/>
-    </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D44" s="5"/>
-    </row>
-    <row r="45" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C45" s="19"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="10"/>
-    </row>
-    <row r="46" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C46" s="19"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="10"/>
-    </row>
-    <row r="47" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C47" s="19"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
-      <c r="N47" s="10"/>
-    </row>
-    <row r="48" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D48" s="5"/>
-    </row>
-    <row r="49" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D49" s="5"/>
-    </row>
-    <row r="50" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D50" s="5"/>
-    </row>
-    <row r="51" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D51" s="5"/>
-    </row>
-    <row r="52" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D52" s="5"/>
-    </row>
-    <row r="53" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D53" s="5"/>
-    </row>
-    <row r="54" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D54" s="5"/>
-    </row>
-    <row r="55" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D55" s="5"/>
-    </row>
-    <row r="56" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D56" s="5"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44ADB29C-CB17-420C-8D8F-0227DF69DE78}">
   <dimension ref="A1:P16"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -5385,7 +4938,7 @@
       <c r="B4" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="19" t="s">
         <v>225</v>
       </c>
       <c r="D4" s="2"/>
@@ -5395,7 +4948,7 @@
       <c r="B5" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="19" t="s">
         <v>226</v>
       </c>
       <c r="P5" s="2"/>
@@ -5404,7 +4957,7 @@
       <c r="B6" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>174</v>
       </c>
       <c r="D6" s="2"/>
@@ -5423,7 +4976,7 @@
       <c r="B7" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="19" t="s">
         <v>173</v>
       </c>
       <c r="D7" s="2"/>
@@ -5442,7 +4995,7 @@
       <c r="B8" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="19" t="s">
         <v>174</v>
       </c>
       <c r="D8" s="2"/>
@@ -5458,7 +5011,7 @@
       <c r="N8" s="5"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C9" s="20"/>
+      <c r="C9" s="19"/>
       <c r="D9" s="2"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -5472,7 +5025,7 @@
       <c r="N9" s="5"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C10" s="20"/>
+      <c r="C10" s="19"/>
       <c r="D10" s="2"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -5530,7 +5083,1244 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D336322D-EE83-4CD8-AE19-906C661F2A7C}">
+  <dimension ref="A1:P68"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" style="14" customWidth="1"/>
+    <col min="2" max="2" width="11.75" style="20" customWidth="1"/>
+    <col min="3" max="3" width="108.5" style="45" customWidth="1"/>
+    <col min="4" max="4" width="10.9140625" style="22" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" style="14" customWidth="1"/>
+    <col min="6" max="6" width="11.75" style="20" customWidth="1"/>
+    <col min="7" max="7" width="19.1640625" style="21" customWidth="1"/>
+    <col min="8" max="8" width="10.9140625" style="11" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" style="14" customWidth="1"/>
+    <col min="10" max="10" width="11.75" style="20" customWidth="1"/>
+    <col min="11" max="11" width="19.1640625" style="21" customWidth="1"/>
+    <col min="12" max="12" width="10.9140625" style="11" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" style="14" customWidth="1"/>
+    <col min="14" max="14" width="11.75" style="20" customWidth="1"/>
+    <col min="15" max="15" width="19.1640625" style="21" customWidth="1"/>
+    <col min="16" max="16" width="12.4140625" style="11" customWidth="1"/>
+    <col min="17" max="18" width="18.1640625" style="11" customWidth="1"/>
+    <col min="19" max="19" width="28.08203125" style="11" customWidth="1"/>
+    <col min="20" max="16384" width="12.33203125" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="27"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:16" s="49" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="46" t="s">
+        <v>277</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="28"/>
+      <c r="B4" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>272</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="28"/>
+      <c r="B5" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="28"/>
+      <c r="B6" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="28"/>
+      <c r="B7" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+    </row>
+    <row r="8" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="28"/>
+      <c r="B8" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="C8" s="42"/>
+      <c r="P8" s="11"/>
+    </row>
+    <row r="9" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="29"/>
+      <c r="B9" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>264</v>
+      </c>
+      <c r="P9" s="11"/>
+    </row>
+    <row r="10" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="29"/>
+      <c r="B10" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>284</v>
+      </c>
+      <c r="O10" s="21"/>
+      <c r="P10" s="11"/>
+    </row>
+    <row r="11" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="29"/>
+      <c r="B11" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>271</v>
+      </c>
+      <c r="O11" s="21"/>
+      <c r="P11" s="11"/>
+    </row>
+    <row r="12" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="29"/>
+      <c r="B12" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="C12" s="42"/>
+      <c r="H12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="11"/>
+    </row>
+    <row r="13" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="29"/>
+      <c r="B13" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C13" s="42"/>
+      <c r="H13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="11"/>
+    </row>
+    <row r="14" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="29"/>
+      <c r="B14" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="C14" s="42"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="11"/>
+    </row>
+    <row r="15" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="29"/>
+      <c r="B15" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="C15" s="42"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="11"/>
+    </row>
+    <row r="16" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="29"/>
+      <c r="B16" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="C16" s="42"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="11"/>
+    </row>
+    <row r="17" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="29"/>
+      <c r="B17" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="C17" s="42"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="11"/>
+    </row>
+    <row r="18" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="C18" s="42"/>
+      <c r="E18" s="11"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="11"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="11"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="11"/>
+    </row>
+    <row r="19" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="28"/>
+      <c r="B19" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="E19" s="11"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="11"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="11"/>
+      <c r="O19" s="21"/>
+      <c r="P19" s="11"/>
+    </row>
+    <row r="20" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="42"/>
+      <c r="E20" s="11"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="11"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="11"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="11"/>
+    </row>
+    <row r="21" spans="1:16" s="20" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="44"/>
+      <c r="E21" s="11"/>
+      <c r="G21" s="21"/>
+      <c r="K21" s="21"/>
+      <c r="O21" s="21"/>
+      <c r="P21" s="11"/>
+    </row>
+    <row r="22" spans="1:16" s="20" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="11"/>
+      <c r="C22" s="45"/>
+      <c r="E22" s="11"/>
+      <c r="G22" s="21"/>
+      <c r="I22" s="11"/>
+      <c r="K22" s="21"/>
+      <c r="M22" s="11"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="11"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A23" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="B23" s="33"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+    </row>
+    <row r="24" spans="1:16" s="49" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="46" t="s">
+        <v>274</v>
+      </c>
+      <c r="B24" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="M25" s="11"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26" s="28"/>
+      <c r="B26" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27" s="28"/>
+      <c r="B27" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A28" s="28"/>
+      <c r="B28" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29" s="28"/>
+      <c r="B29" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30" s="28"/>
+      <c r="B30" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="C30" s="42"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" s="29"/>
+      <c r="B31" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="C31" s="42"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" s="28"/>
+      <c r="B32" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="C32" s="42"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" s="28"/>
+      <c r="B33" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="C33" s="42"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" s="29"/>
+      <c r="B34" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="C34" s="42"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" s="29"/>
+      <c r="B35" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="C35" s="42" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" s="29"/>
+      <c r="B36" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="C36" s="42" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" s="29"/>
+      <c r="B37" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="C37" s="42"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="C38" s="42"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="42"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="42"/>
+    </row>
+    <row r="41" spans="1:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="44"/>
+    </row>
+    <row r="42" spans="1:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43" s="35" t="s">
+        <v>279</v>
+      </c>
+      <c r="B43" s="36"/>
+      <c r="C43" s="37"/>
+    </row>
+    <row r="44" spans="1:13" s="49" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="46" t="s">
+        <v>236</v>
+      </c>
+      <c r="B44" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" s="50"/>
+      <c r="E44" s="51"/>
+      <c r="I44" s="51"/>
+      <c r="M44" s="51"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A45" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="42" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46" s="28"/>
+      <c r="B46" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="C46" s="42" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47" s="38"/>
+      <c r="B47" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="C47" s="42"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A48" s="38"/>
+      <c r="B48" s="23" t="s">
+        <v>268</v>
+      </c>
+      <c r="C48" s="42" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A49" s="28"/>
+      <c r="B49" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="C49" s="42"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A50" s="28"/>
+      <c r="B50" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="C50" s="42"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A51" s="28"/>
+      <c r="B51" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="C51" s="42"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A52" s="28"/>
+      <c r="B52" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="C52" s="42"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A53" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="C53" s="42"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A54" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="42" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A55" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" s="42"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A56" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" s="42"/>
+    </row>
+    <row r="57" spans="1:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="B57" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="C57" s="44"/>
+    </row>
+    <row r="58" spans="1:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A59" s="39" t="s">
+        <v>280</v>
+      </c>
+      <c r="B59" s="40"/>
+      <c r="C59" s="41"/>
+    </row>
+    <row r="60" spans="1:13" s="49" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="46" t="s">
+        <v>248</v>
+      </c>
+      <c r="B60" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D60" s="50"/>
+      <c r="E60" s="51"/>
+      <c r="I60" s="51"/>
+      <c r="M60" s="51"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A61" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B61" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" s="42" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A62" s="28"/>
+      <c r="B62" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="C62" s="42" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A63" s="28"/>
+      <c r="B63" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="C63" s="42" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A64" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B64" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="C64" s="42"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="42" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B66" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66" s="42"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B67" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C67" s="42"/>
+    </row>
+    <row r="68" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="B68" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="C68" s="44" t="s">
+        <v>174</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A59:C59"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBFDA69-2E4B-4796-8839-B70CBD0249B0}">
+  <dimension ref="A1:P42"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="11.75" style="5" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.9140625" customWidth="1"/>
+    <col min="5" max="8" width="10.9140625" style="2" customWidth="1"/>
+    <col min="9" max="11" width="10.75" style="2" customWidth="1"/>
+    <col min="12" max="13" width="9.83203125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="14" style="2" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="12.4140625" style="2" customWidth="1"/>
+    <col min="17" max="18" width="18.1640625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="28.08203125" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="12.33203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="P3" s="2"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="P8" s="2"/>
+    </row>
+    <row r="9" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15"/>
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15"/>
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15"/>
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="15"/>
+      <c r="C12" s="12"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="P12" s="2"/>
+    </row>
+    <row r="13" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="15"/>
+      <c r="C13" s="12"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="15"/>
+      <c r="C14" s="12"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="P14" s="2"/>
+    </row>
+    <row r="15" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="15"/>
+      <c r="C15" s="12"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="P15" s="2"/>
+    </row>
+    <row r="16" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="15"/>
+      <c r="C16" s="12"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="P16" s="2"/>
+    </row>
+    <row r="17" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="15"/>
+      <c r="C17" s="12"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="P17" s="2"/>
+    </row>
+    <row r="18" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="15"/>
+      <c r="C18" s="12"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="P18" s="2"/>
+    </row>
+    <row r="19" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="15"/>
+      <c r="C19" s="12"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="P19" s="2"/>
+    </row>
+    <row r="20" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="15"/>
+      <c r="C20" s="12"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="P20" s="2"/>
+    </row>
+    <row r="21" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="15"/>
+      <c r="C21" s="12"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="P21" s="2"/>
+    </row>
+    <row r="22" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="15"/>
+      <c r="P22" s="2"/>
+    </row>
+    <row r="23" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="15"/>
+      <c r="P23" s="2"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C24" s="5"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C25" s="5"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C26" s="5"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C27" s="5"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C28" s="5"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C29" s="5"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C30" s="5"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C31" s="10"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C32" s="10"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+    </row>
+    <row r="33" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C33" s="10"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+    </row>
+    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C34" s="5"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+    </row>
+    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C35" s="5"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+    </row>
+    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C36" s="5"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+    </row>
+    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C37" s="5"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+    </row>
+    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D38" s="2"/>
+    </row>
+    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D39" s="2"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+    </row>
+    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D40" s="2"/>
+    </row>
+    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D41" s="2"/>
+    </row>
+    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D42" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50E289C6-4857-403B-BCF4-4E6CA413AF65}">
   <dimension ref="A1:S58"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -6147,4 +6937,367 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33906C0D-BD2E-46FD-BACB-143C3F60348C}">
+  <dimension ref="A1:N59"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="11.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="85.6640625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="10.9140625" style="4" customWidth="1"/>
+    <col min="5" max="8" width="10.9140625" style="5" customWidth="1"/>
+    <col min="9" max="11" width="10.75" style="5" customWidth="1"/>
+    <col min="12" max="13" width="9.83203125" style="5" customWidth="1"/>
+    <col min="14" max="14" width="14" style="5" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" style="5" customWidth="1"/>
+    <col min="16" max="16" width="12.4140625" style="5" customWidth="1"/>
+    <col min="17" max="18" width="18.1640625" style="5" customWidth="1"/>
+    <col min="19" max="19" width="28.08203125" style="5" customWidth="1"/>
+    <col min="20" max="16384" width="12.33203125" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="5"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D23" s="5"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B26" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D26" s="5"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B27" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D29" s="5"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="D30" s="5"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D31" s="5"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="5"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="5"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D34" s="5"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D35" s="5"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D36" s="5"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D37" s="5"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D38" s="5"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D39" s="5"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D40" s="5"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D41" s="5"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D42" s="5"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D43" s="5"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D44" s="5"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D45" s="5"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D46" s="5"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D47" s="5"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C48" s="18"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C49" s="18"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C50" s="18"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="10"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D51" s="5"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D52" s="5"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D53" s="5"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D54" s="5"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D55" s="5"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D56" s="5"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D57" s="5"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D58" s="5"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D59" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/系统开发字段说明.xlsx
+++ b/系统开发字段说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kongf\Desktop\集运系统\JIYUN-ADMIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4652BC77-AB62-4588-AD11-7046CFA1EE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41139A58-B4AE-40FD-9380-3FA267E77D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37680" yWindow="3285" windowWidth="38640" windowHeight="21240" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16420" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="包裹状态字典" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="285">
   <si>
     <t>字段：</t>
   </si>
@@ -851,9 +851,6 @@
     <t>航线代码</t>
   </si>
   <si>
-    <t>必填</t>
-  </si>
-  <si>
     <t>必选：是/否</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -898,10 +895,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>提单号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>发货人</t>
   </si>
   <si>
@@ -972,10 +965,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>唯一，选填</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>班(航)次名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1021,6 +1010,18 @@
   </si>
   <si>
     <t>必填，默认为关系班(航)的&lt;目的港&gt;；如果关联的&lt;班(航)次&gt;的&lt;目的港&gt;为：aa/bb则需要选择“aa”/“bb”；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提(运)单号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提(运)单ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按照创建的时间自动生成,12位数字，唯一</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1347,18 +1348,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1371,35 +1360,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1430,6 +1392,45 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3788,13 +3789,13 @@
       <c r="C3" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
       <c r="I3" s="13" t="s">
         <v>173</v>
       </c>
@@ -5085,12 +5086,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D336322D-EE83-4CD8-AE19-906C661F2A7C}">
-  <dimension ref="A1:P68"/>
+  <dimension ref="A1:P69"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.83203125" style="14" customWidth="1"/>
     <col min="2" max="2" width="11.75" style="20" customWidth="1"/>
-    <col min="3" max="3" width="108.5" style="45" customWidth="1"/>
+    <col min="3" max="3" width="108.5" style="32" customWidth="1"/>
     <col min="4" max="4" width="10.9140625" style="22" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" style="14" customWidth="1"/>
     <col min="6" max="6" width="11.75" style="20" customWidth="1"/>
@@ -5110,11 +5111,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
-        <v>276</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="27"/>
+      <c r="A1" s="39" t="s">
+        <v>273</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="41"/>
       <c r="E1" s="11"/>
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
@@ -5122,25 +5123,25 @@
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
     </row>
-    <row r="2" spans="1:16" s="49" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="46" t="s">
-        <v>277</v>
-      </c>
-      <c r="B2" s="47" t="s">
+    <row r="2" spans="1:16" s="36" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="33" t="s">
+        <v>274</v>
+      </c>
+      <c r="B2" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="29" t="s">
         <v>23</v>
       </c>
       <c r="D3" s="11"/>
@@ -5152,12 +5153,12 @@
       <c r="K3" s="11"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="28"/>
+      <c r="A4" s="24"/>
       <c r="B4" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="C4" s="42" t="s">
-        <v>272</v>
+        <v>283</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>284</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -5168,12 +5169,12 @@
       <c r="K4" s="11"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="28"/>
+      <c r="A5" s="24"/>
       <c r="B5" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>240</v>
+        <v>282</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>185</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -5184,13 +5185,11 @@
       <c r="K5" s="11"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="28"/>
+      <c r="A6" s="24"/>
       <c r="B6" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="C6" s="42" t="s">
-        <v>240</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="C6" s="29"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
@@ -5200,13 +5199,11 @@
       <c r="K6" s="11"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="28"/>
+      <c r="A7" s="24"/>
       <c r="B7" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="C7" s="42" t="s">
-        <v>240</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="C7" s="29"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
@@ -5215,88 +5212,88 @@
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
     </row>
-    <row r="8" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="28"/>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" s="24"/>
       <c r="B8" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" s="29"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+    </row>
+    <row r="9" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="24"/>
+      <c r="B9" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="C9" s="29"/>
+      <c r="P9" s="11"/>
+    </row>
+    <row r="10" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="25"/>
+      <c r="B10" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="C10" s="29" t="s">
         <v>262</v>
       </c>
-      <c r="C8" s="42"/>
-      <c r="P8" s="11"/>
-    </row>
-    <row r="9" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="29"/>
-      <c r="B9" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="C9" s="42" t="s">
-        <v>264</v>
-      </c>
-      <c r="P9" s="11"/>
-    </row>
-    <row r="10" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="29"/>
-      <c r="B10" s="23" t="s">
-        <v>260</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>284</v>
-      </c>
-      <c r="O10" s="21"/>
       <c r="P10" s="11"/>
     </row>
     <row r="11" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="29"/>
+      <c r="A11" s="25"/>
       <c r="B11" s="23" t="s">
-        <v>265</v>
-      </c>
-      <c r="C11" s="42" t="s">
-        <v>271</v>
+        <v>258</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>281</v>
       </c>
       <c r="O11" s="21"/>
       <c r="P11" s="11"/>
     </row>
     <row r="12" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="29"/>
+      <c r="A12" s="25"/>
       <c r="B12" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="C12" s="42"/>
-      <c r="H12" s="11"/>
-      <c r="L12" s="11"/>
+        <v>263</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>269</v>
+      </c>
       <c r="O12" s="21"/>
       <c r="P12" s="11"/>
     </row>
     <row r="13" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="29"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="C13" s="42"/>
+        <v>264</v>
+      </c>
+      <c r="C13" s="29"/>
       <c r="H13" s="11"/>
       <c r="L13" s="11"/>
       <c r="O13" s="21"/>
       <c r="P13" s="11"/>
     </row>
     <row r="14" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="29"/>
+      <c r="A14" s="25"/>
       <c r="B14" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="C14" s="42"/>
+        <v>202</v>
+      </c>
+      <c r="C14" s="29"/>
       <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="K14" s="21"/>
       <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
       <c r="O14" s="21"/>
       <c r="P14" s="11"/>
     </row>
     <row r="15" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="29"/>
+      <c r="A15" s="25"/>
       <c r="B15" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="C15" s="42"/>
+        <v>203</v>
+      </c>
+      <c r="C15" s="29"/>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="K15" s="21"/>
@@ -5306,11 +5303,11 @@
       <c r="P15" s="11"/>
     </row>
     <row r="16" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="29"/>
+      <c r="A16" s="25"/>
       <c r="B16" s="23" t="s">
-        <v>267</v>
-      </c>
-      <c r="C16" s="42"/>
+        <v>206</v>
+      </c>
+      <c r="C16" s="29"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="K16" s="21"/>
@@ -5320,11 +5317,11 @@
       <c r="P16" s="11"/>
     </row>
     <row r="17" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="29"/>
+      <c r="A17" s="25"/>
       <c r="B17" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="C17" s="42"/>
+        <v>265</v>
+      </c>
+      <c r="C17" s="29"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="K17" s="21"/>
@@ -5334,29 +5331,27 @@
       <c r="P17" s="11"/>
     </row>
     <row r="18" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="28" t="s">
-        <v>8</v>
-      </c>
+      <c r="A18" s="25"/>
       <c r="B18" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="C18" s="42"/>
-      <c r="E18" s="11"/>
-      <c r="G18" s="21"/>
+        <v>259</v>
+      </c>
+      <c r="C18" s="29"/>
       <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
       <c r="K18" s="21"/>
       <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
       <c r="O18" s="21"/>
       <c r="P18" s="11"/>
     </row>
     <row r="19" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
+      <c r="A19" s="24" t="s">
+        <v>8</v>
+      </c>
       <c r="B19" s="23" t="s">
-        <v>275</v>
-      </c>
-      <c r="C19" s="42" t="s">
-        <v>281</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="C19" s="29"/>
       <c r="E19" s="11"/>
       <c r="G19" s="21"/>
       <c r="H19" s="11"/>
@@ -5366,13 +5361,13 @@
       <c r="P19" s="11"/>
     </row>
     <row r="20" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="28" t="s">
-        <v>9</v>
-      </c>
+      <c r="A20" s="24"/>
       <c r="B20" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="42"/>
+        <v>272</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>278</v>
+      </c>
       <c r="E20" s="11"/>
       <c r="G20" s="21"/>
       <c r="H20" s="11"/>
@@ -5381,442 +5376,458 @@
       <c r="O20" s="21"/>
       <c r="P20" s="11"/>
     </row>
-    <row r="21" spans="1:16" s="20" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="44"/>
+    <row r="21" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="29"/>
       <c r="E21" s="11"/>
       <c r="G21" s="21"/>
+      <c r="H21" s="11"/>
       <c r="K21" s="21"/>
+      <c r="L21" s="11"/>
       <c r="O21" s="21"/>
       <c r="P21" s="11"/>
     </row>
     <row r="22" spans="1:16" s="20" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="11"/>
-      <c r="C22" s="45"/>
+      <c r="A22" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="31"/>
       <c r="E22" s="11"/>
       <c r="G22" s="21"/>
-      <c r="I22" s="11"/>
       <c r="K22" s="21"/>
-      <c r="M22" s="11"/>
       <c r="O22" s="21"/>
       <c r="P22" s="11"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="B23" s="33"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20"/>
-    </row>
-    <row r="24" spans="1:16" s="49" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="46" t="s">
-        <v>274</v>
-      </c>
-      <c r="B24" s="47" t="s">
+    <row r="23" spans="1:16" s="20" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="11"/>
+      <c r="C23" s="32"/>
+      <c r="E23" s="11"/>
+      <c r="G23" s="21"/>
+      <c r="I23" s="11"/>
+      <c r="K23" s="21"/>
+      <c r="M23" s="11"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="11"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="B24" s="43"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+    </row>
+    <row r="25" spans="1:16" s="36" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="B25" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="48" t="s">
+      <c r="C25" s="35" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" s="28" t="s">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B26" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="42" t="s">
+      <c r="C26" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="E25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="M25" s="11"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A26" s="28"/>
-      <c r="B26" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="C26" s="42" t="s">
+      <c r="E26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="M26" s="11"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27" s="24"/>
+      <c r="B27" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A28" s="24"/>
+      <c r="B28" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29" s="24"/>
+      <c r="B29" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="C29" s="29" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30" s="24"/>
+      <c r="B30" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="C30" s="29" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" s="24"/>
+      <c r="B31" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="C31" s="29"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" s="25"/>
+      <c r="B32" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="C32" s="29"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" s="24"/>
+      <c r="B33" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="C33" s="29"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" s="24"/>
+      <c r="B34" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="C34" s="29"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" s="25"/>
+      <c r="B35" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="C35" s="29"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" s="25"/>
+      <c r="B36" s="23" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A27" s="28"/>
-      <c r="B27" s="23" t="s">
-        <v>256</v>
-      </c>
-      <c r="C27" s="42" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A28" s="28"/>
-      <c r="B28" s="23" t="s">
-        <v>242</v>
-      </c>
-      <c r="C28" s="42" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A29" s="28"/>
-      <c r="B29" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="C29" s="42" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A30" s="28"/>
-      <c r="B30" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="C30" s="42"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A31" s="29"/>
-      <c r="B31" s="23" t="s">
-        <v>245</v>
-      </c>
-      <c r="C31" s="42"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A32" s="28"/>
-      <c r="B32" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="C32" s="42"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="28"/>
-      <c r="B33" s="23" t="s">
+      <c r="C36" s="29" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" s="25"/>
+      <c r="B37" s="23" t="s">
         <v>258</v>
       </c>
-      <c r="C33" s="42"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" s="29"/>
-      <c r="B34" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="C34" s="42"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="29"/>
-      <c r="B35" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="C35" s="42" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="29"/>
-      <c r="B36" s="23" t="s">
-        <v>260</v>
-      </c>
-      <c r="C36" s="42" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" s="29"/>
-      <c r="B37" s="23" t="s">
+      <c r="C37" s="29" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" s="25"/>
+      <c r="B38" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="C37" s="42"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" s="28" t="s">
+      <c r="C38" s="29"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="23" t="s">
+      <c r="B39" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="C38" s="42"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A39" s="28" t="s">
+      <c r="C39" s="29"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B39" s="23" t="s">
+      <c r="B40" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="42"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A40" s="28" t="s">
+      <c r="C40" s="29"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B40" s="23" t="s">
+      <c r="B41" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C40" s="42"/>
-    </row>
-    <row r="41" spans="1:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="30" t="s">
+      <c r="C41" s="29"/>
+    </row>
+    <row r="42" spans="1:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B41" s="31" t="s">
+      <c r="B42" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C41" s="44"/>
-    </row>
-    <row r="42" spans="1:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="35" t="s">
-        <v>279</v>
-      </c>
-      <c r="B43" s="36"/>
-      <c r="C43" s="37"/>
-    </row>
-    <row r="44" spans="1:13" s="49" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="46" t="s">
+      <c r="C42" s="31"/>
+    </row>
+    <row r="43" spans="1:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44" s="45" t="s">
+        <v>276</v>
+      </c>
+      <c r="B44" s="46"/>
+      <c r="C44" s="47"/>
+    </row>
+    <row r="45" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="33" t="s">
         <v>236</v>
       </c>
-      <c r="B44" s="47" t="s">
+      <c r="B45" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C44" s="48" t="s">
+      <c r="C45" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="D44" s="50"/>
-      <c r="E44" s="51"/>
-      <c r="I44" s="51"/>
-      <c r="M44" s="51"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" s="28" t="s">
+      <c r="D45" s="37"/>
+      <c r="E45" s="38"/>
+      <c r="I45" s="38"/>
+      <c r="M45" s="38"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B45" s="23" t="s">
+      <c r="B46" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C45" s="42" t="s">
+      <c r="C46" s="29" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="28"/>
-      <c r="B46" s="23" t="s">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47" s="24"/>
+      <c r="B47" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="C46" s="42" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="38"/>
-      <c r="B47" s="23" t="s">
+      <c r="C47" s="29" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A48" s="28"/>
+      <c r="B48" s="23" t="s">
         <v>239</v>
       </c>
-      <c r="C47" s="42"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="38"/>
-      <c r="B48" s="23" t="s">
-        <v>268</v>
-      </c>
-      <c r="C48" s="42" t="s">
-        <v>269</v>
-      </c>
+      <c r="C48" s="29"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="28"/>
       <c r="B49" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="C49" s="42"/>
+        <v>266</v>
+      </c>
+      <c r="C49" s="29" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A50" s="28"/>
+      <c r="A50" s="24"/>
       <c r="B50" s="23" t="s">
+        <v>268</v>
+      </c>
+      <c r="C50" s="29"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A51" s="24"/>
+      <c r="B51" s="23" t="s">
         <v>238</v>
       </c>
-      <c r="C50" s="42"/>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A51" s="28"/>
-      <c r="B51" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="C51" s="42"/>
+      <c r="C51" s="29"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A52" s="28"/>
+      <c r="A52" s="24"/>
       <c r="B52" s="23" t="s">
-        <v>260</v>
-      </c>
-      <c r="C52" s="42"/>
+        <v>257</v>
+      </c>
+      <c r="C52" s="29"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A53" s="28" t="s">
+      <c r="A53" s="24"/>
+      <c r="B53" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="C53" s="29"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A54" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B53" s="23" t="s">
+      <c r="B54" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="C53" s="42"/>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A54" s="28" t="s">
+      <c r="C54" s="29"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A55" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B54" s="23" t="s">
+      <c r="B55" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="42" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A55" s="28" t="s">
+      <c r="C55" s="29" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A56" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B55" s="23" t="s">
+      <c r="B56" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C55" s="42"/>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A56" s="28" t="s">
+      <c r="C56" s="29"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A57" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B56" s="23" t="s">
+      <c r="B57" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C56" s="42"/>
-    </row>
-    <row r="57" spans="1:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="30" t="s">
+      <c r="C57" s="29"/>
+    </row>
+    <row r="58" spans="1:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="B57" s="31" t="s">
+      <c r="B58" s="27" t="s">
         <v>233</v>
       </c>
-      <c r="C57" s="44"/>
-    </row>
-    <row r="58" spans="1:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A59" s="39" t="s">
-        <v>280</v>
-      </c>
-      <c r="B59" s="40"/>
-      <c r="C59" s="41"/>
-    </row>
-    <row r="60" spans="1:13" s="49" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="46" t="s">
+      <c r="C58" s="31"/>
+    </row>
+    <row r="59" spans="1:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A60" s="48" t="s">
+        <v>277</v>
+      </c>
+      <c r="B60" s="49"/>
+      <c r="C60" s="50"/>
+    </row>
+    <row r="61" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="B61" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D61" s="37"/>
+      <c r="E61" s="38"/>
+      <c r="I61" s="38"/>
+      <c r="M61" s="38"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A62" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B62" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" s="29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A63" s="24"/>
+      <c r="B63" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="B60" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="C60" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D60" s="50"/>
-      <c r="E60" s="51"/>
-      <c r="I60" s="51"/>
-      <c r="M60" s="51"/>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A61" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="B61" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61" s="42" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A62" s="28"/>
-      <c r="B62" s="23" t="s">
+      <c r="C63" s="29" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A64" s="24"/>
+      <c r="B64" s="23" t="s">
         <v>249</v>
       </c>
-      <c r="C62" s="42" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A63" s="28"/>
-      <c r="B63" s="23" t="s">
+      <c r="C64" s="29" t="s">
         <v>250</v>
       </c>
-      <c r="C63" s="42" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A64" s="28" t="s">
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B64" s="23" t="s">
+      <c r="B65" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="C64" s="42"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="28" t="s">
+      <c r="C65" s="29"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B65" s="23" t="s">
+      <c r="B66" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C65" s="42" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="28" t="s">
+      <c r="C66" s="29" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B66" s="23" t="s">
+      <c r="B67" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C66" s="42"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="28" t="s">
+      <c r="C67" s="29"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B67" s="23" t="s">
+      <c r="B68" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C67" s="42"/>
-    </row>
-    <row r="68" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="30" t="s">
+      <c r="C68" s="29"/>
+    </row>
+    <row r="69" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="B68" s="31" t="s">
+      <c r="B69" s="27" t="s">
         <v>233</v>
       </c>
-      <c r="C68" s="44" t="s">
+      <c r="C69" s="31" t="s">
         <v>174</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A60:C60"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/系统开发字段说明.xlsx
+++ b/系统开发字段说明.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kongf\Desktop\集运系统\JIYUN-ADMIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41139A58-B4AE-40FD-9380-3FA267E77D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC6D097-78A6-44FF-8B5F-FA4BE495698A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16420" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16420" tabRatio="786" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="包裹状态字典" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,12 @@
     <sheet name="标签管理" sheetId="6" r:id="rId3"/>
     <sheet name="单号库" sheetId="7" r:id="rId4"/>
     <sheet name="地址簿" sheetId="9" r:id="rId5"/>
-    <sheet name="航线运输管理" sheetId="11" r:id="rId6"/>
-    <sheet name="渠道管理" sheetId="5" r:id="rId7"/>
-    <sheet name="第三方派送" sheetId="10" r:id="rId8"/>
-    <sheet name="运单管理" sheetId="8" r:id="rId9"/>
-    <sheet name="代购订单管理" sheetId="4" r:id="rId10"/>
+    <sheet name="证件管理" sheetId="12" r:id="rId6"/>
+    <sheet name="航线运输管理" sheetId="11" r:id="rId7"/>
+    <sheet name="渠道管理" sheetId="5" r:id="rId8"/>
+    <sheet name="第三方派送" sheetId="10" r:id="rId9"/>
+    <sheet name="运单管理" sheetId="8" r:id="rId10"/>
+    <sheet name="代购订单管理" sheetId="4" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2991,6 +2992,369 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33906C0D-BD2E-46FD-BACB-143C3F60348C}">
+  <dimension ref="A1:N59"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="11.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="85.6640625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="10.9140625" style="4" customWidth="1"/>
+    <col min="5" max="8" width="10.9140625" style="5" customWidth="1"/>
+    <col min="9" max="11" width="10.75" style="5" customWidth="1"/>
+    <col min="12" max="13" width="9.83203125" style="5" customWidth="1"/>
+    <col min="14" max="14" width="14" style="5" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" style="5" customWidth="1"/>
+    <col min="16" max="16" width="12.4140625" style="5" customWidth="1"/>
+    <col min="17" max="18" width="18.1640625" style="5" customWidth="1"/>
+    <col min="19" max="19" width="28.08203125" style="5" customWidth="1"/>
+    <col min="20" max="16384" width="12.33203125" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="5"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D23" s="5"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B26" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D26" s="5"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B27" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D29" s="5"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="D30" s="5"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D31" s="5"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="5"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="5"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D34" s="5"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D35" s="5"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D36" s="5"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D37" s="5"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D38" s="5"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D39" s="5"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D40" s="5"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D41" s="5"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D42" s="5"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D43" s="5"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D44" s="5"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D45" s="5"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D46" s="5"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D47" s="5"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C48" s="18"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C49" s="18"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C50" s="18"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="10"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D51" s="5"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D52" s="5"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D53" s="5"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D54" s="5"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D55" s="5"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D56" s="5"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D57" s="5"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D58" s="5"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D59" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67522C72-12D8-48E2-AD4C-816A16959AA6}">
   <dimension ref="A1:S58"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -5085,6 +5449,17 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16523A7D-4EF0-4520-A367-1CA33F33FB12}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D336322D-EE83-4CD8-AE19-906C661F2A7C}">
   <dimension ref="A1:P69"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -5835,7 +6210,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBFDA69-2E4B-4796-8839-B70CBD0249B0}">
   <dimension ref="A1:P42"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -6331,7 +6706,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50E289C6-4857-403B-BCF4-4E6CA413AF65}">
   <dimension ref="A1:S58"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -6948,367 +7323,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33906C0D-BD2E-46FD-BACB-143C3F60348C}">
-  <dimension ref="A1:N59"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.33203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="11.75" style="3" customWidth="1"/>
-    <col min="3" max="3" width="85.6640625" style="12" customWidth="1"/>
-    <col min="4" max="4" width="10.9140625" style="4" customWidth="1"/>
-    <col min="5" max="8" width="10.9140625" style="5" customWidth="1"/>
-    <col min="9" max="11" width="10.75" style="5" customWidth="1"/>
-    <col min="12" max="13" width="9.83203125" style="5" customWidth="1"/>
-    <col min="14" max="14" width="14" style="5" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" style="5" customWidth="1"/>
-    <col min="16" max="16" width="12.4140625" style="5" customWidth="1"/>
-    <col min="17" max="18" width="18.1640625" style="5" customWidth="1"/>
-    <col min="19" max="19" width="28.08203125" style="5" customWidth="1"/>
-    <col min="20" max="16384" width="12.33203125" style="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="5"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="5"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="D3" s="5"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B11" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B13" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B15" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B16" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D17" s="5"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D18" s="5"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B19" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="D19" s="5"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B20" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B21" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="D21" s="5"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B22" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D22" s="5"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D23" s="5"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B24" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="D24" s="5"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D25" s="5"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B26" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D26" s="5"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B27" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D27" s="5"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D28" s="5"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B29" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D29" s="5"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B30" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="D30" s="5"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D31" s="5"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="5"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D33" s="5"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D34" s="5"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D35" s="5"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D36" s="5"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D37" s="5"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D38" s="5"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D39" s="5"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D40" s="5"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D41" s="5"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D42" s="5"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D43" s="5"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D44" s="5"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D45" s="5"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D46" s="5"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D47" s="5"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C48" s="18"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
-      <c r="N48" s="10"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C49" s="18"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="10"/>
-      <c r="M49" s="10"/>
-      <c r="N49" s="10"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C50" s="18"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="10"/>
-      <c r="M50" s="10"/>
-      <c r="N50" s="10"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D51" s="5"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D52" s="5"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D53" s="5"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D54" s="5"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D55" s="5"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D56" s="5"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D57" s="5"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D58" s="5"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D59" s="5"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/系统开发字段说明.xlsx
+++ b/系统开发字段说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kongf\Desktop\集运系统\JIYUN-ADMIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC6D097-78A6-44FF-8B5F-FA4BE495698A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8454B1F3-5FDE-4C73-AA57-32A3ED0728FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16420" tabRatio="786" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16420" tabRatio="786" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="包裹状态字典" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="第三方派送" sheetId="10" r:id="rId9"/>
     <sheet name="运单管理" sheetId="8" r:id="rId10"/>
     <sheet name="代购订单管理" sheetId="4" r:id="rId11"/>
+    <sheet name="包裹管理" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="346">
   <si>
     <t>字段：</t>
   </si>
@@ -1024,6 +1025,189 @@
   <si>
     <t>按照创建的时间自动生成,12位数字，唯一</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>字段名</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>约束/索引</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>PK, AUTO_INCREMENT</t>
+  </si>
+  <si>
+    <t>包裹ID</t>
+  </si>
+  <si>
+    <t>user_id</t>
+  </si>
+  <si>
+    <t>所属用户ID（可空，入库时为 NULL）</t>
+  </si>
+  <si>
+    <t>tracking_number</t>
+  </si>
+  <si>
+    <t>VARCHAR(128)</t>
+  </si>
+  <si>
+    <t>包裹单号（唯一）</t>
+  </si>
+  <si>
+    <t>origin</t>
+  </si>
+  <si>
+    <t>VARCHAR(255)</t>
+  </si>
+  <si>
+    <t>NOT NULL</t>
+  </si>
+  <si>
+    <t>来源</t>
+  </si>
+  <si>
+    <t>destination</t>
+  </si>
+  <si>
+    <t>目的地</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>DOUBLE</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>重量（可空）</t>
+  </si>
+  <si>
+    <t>length_cm</t>
+  </si>
+  <si>
+    <t>长度（可空，单位 cm）</t>
+  </si>
+  <si>
+    <t>width_cm</t>
+  </si>
+  <si>
+    <t>宽度（可空，单位 cm）</t>
+  </si>
+  <si>
+    <t>height_cm</t>
+  </si>
+  <si>
+    <t>高度（可空，单位 cm）</t>
+  </si>
+  <si>
+    <t>volume</t>
+  </si>
+  <si>
+    <t>体积（可空）</t>
+  </si>
+  <si>
+    <t>images</t>
+  </si>
+  <si>
+    <t>TEXT</t>
+  </si>
+  <si>
+    <t>图片URL列表（逗号分隔，可空，支持多张）</t>
+  </si>
+  <si>
+    <t>shelf_location</t>
+  </si>
+  <si>
+    <t>VARCHAR(64)</t>
+  </si>
+  <si>
+    <t>DEFAULT NULL</t>
+  </si>
+  <si>
+    <t>货架位置（可空）</t>
+  </si>
+  <si>
+    <t>库位号（可空，自由文本）</t>
+  </si>
+  <si>
+    <t>sender_address_id</t>
+  </si>
+  <si>
+    <t>recipient_address_id</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>货物态（包裹主状态）</t>
+  </si>
+  <si>
+    <t>sub_status</t>
+  </si>
+  <si>
+    <t>信息态（包裹子状态，可空）</t>
+  </si>
+  <si>
+    <t>DATETIME</t>
+  </si>
+  <si>
+    <t>estimated_delivery</t>
+  </si>
+  <si>
+    <t>预计送达时间（可空）</t>
+  </si>
+  <si>
+    <t>DEFAULT CURRENT_TIMESTAMP</t>
+  </si>
+  <si>
+    <t>DEFAULT CURRENT_TIMESTAMP ON UPDATE CURRENT_TIMESTAMP</t>
+  </si>
+  <si>
+    <t>deleted_at</t>
+  </si>
+  <si>
+    <t>软删除时间（NULL=未删除）</t>
+  </si>
+  <si>
+    <t>2.4 parcels（包裹表）</t>
+  </si>
+  <si>
+    <t>DEFAULT NULL, INDEX idx_parcels_user, FK → users.id ON DELETE SET NULL</t>
+  </si>
+  <si>
+    <t>UNIQUE, NOT NULL, INDEX idx_parcels_tracking</t>
+  </si>
+  <si>
+    <t>绑定物流商ID（可空，逻辑关联 logistics_providers.id）</t>
+  </si>
+  <si>
+    <t>DEFAULT NULL, INDEX idx_parcels_sender_address</t>
+  </si>
+  <si>
+    <t>发货人地址ID（可空，逻辑关联 address_book.id）</t>
+  </si>
+  <si>
+    <t>DEFAULT NULL, INDEX idx_parcels_recipient_address</t>
+  </si>
+  <si>
+    <t>收货人地址ID（可空，逻辑关联 address_book.id）</t>
+  </si>
+  <si>
+    <t>DEFAULT 'pending', INDEX idx_parcels_status</t>
+  </si>
+  <si>
+    <t>DEFAULT NULL, INDEX idx_parcels_sub_status</t>
   </si>
 </sst>
 </file>
@@ -1394,6 +1578,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1429,9 +1616,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4005,6 +4189,351 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14B3504F-3FC9-4808-A798-0586763EC0E3}">
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.4140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="64.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.9140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C4" t="s">
+        <v>337</v>
+      </c>
+      <c r="D4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C5" t="s">
+        <v>338</v>
+      </c>
+      <c r="D5" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>297</v>
+      </c>
+      <c r="B6" t="s">
+        <v>298</v>
+      </c>
+      <c r="C6" t="s">
+        <v>299</v>
+      </c>
+      <c r="D6" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B7" t="s">
+        <v>298</v>
+      </c>
+      <c r="C7" t="s">
+        <v>299</v>
+      </c>
+      <c r="D7" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>303</v>
+      </c>
+      <c r="B8" t="s">
+        <v>304</v>
+      </c>
+      <c r="C8" t="s">
+        <v>305</v>
+      </c>
+      <c r="D8" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>307</v>
+      </c>
+      <c r="B9" t="s">
+        <v>304</v>
+      </c>
+      <c r="C9" t="s">
+        <v>305</v>
+      </c>
+      <c r="D9" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>309</v>
+      </c>
+      <c r="B10" t="s">
+        <v>304</v>
+      </c>
+      <c r="C10" t="s">
+        <v>305</v>
+      </c>
+      <c r="D10" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>311</v>
+      </c>
+      <c r="B11" t="s">
+        <v>304</v>
+      </c>
+      <c r="C11" t="s">
+        <v>305</v>
+      </c>
+      <c r="D11" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>313</v>
+      </c>
+      <c r="B12" t="s">
+        <v>304</v>
+      </c>
+      <c r="C12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D12" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>315</v>
+      </c>
+      <c r="B13" t="s">
+        <v>316</v>
+      </c>
+      <c r="C13" t="s">
+        <v>305</v>
+      </c>
+      <c r="D13" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>318</v>
+      </c>
+      <c r="B14" t="s">
+        <v>319</v>
+      </c>
+      <c r="C14" t="s">
+        <v>320</v>
+      </c>
+      <c r="D14" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>175</v>
+      </c>
+      <c r="B15" t="s">
+        <v>319</v>
+      </c>
+      <c r="C15" t="s">
+        <v>320</v>
+      </c>
+      <c r="D15" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>232</v>
+      </c>
+      <c r="B16" t="s">
+        <v>289</v>
+      </c>
+      <c r="C16" t="s">
+        <v>320</v>
+      </c>
+      <c r="D16" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>323</v>
+      </c>
+      <c r="B17" t="s">
+        <v>289</v>
+      </c>
+      <c r="C17" t="s">
+        <v>340</v>
+      </c>
+      <c r="D17" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>324</v>
+      </c>
+      <c r="B18" t="s">
+        <v>289</v>
+      </c>
+      <c r="C18" t="s">
+        <v>342</v>
+      </c>
+      <c r="D18" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>325</v>
+      </c>
+      <c r="B19" t="s">
+        <v>319</v>
+      </c>
+      <c r="C19" t="s">
+        <v>344</v>
+      </c>
+      <c r="D19" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>327</v>
+      </c>
+      <c r="B20" t="s">
+        <v>319</v>
+      </c>
+      <c r="C20" t="s">
+        <v>345</v>
+      </c>
+      <c r="D20" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>330</v>
+      </c>
+      <c r="B21" t="s">
+        <v>329</v>
+      </c>
+      <c r="C21" t="s">
+        <v>305</v>
+      </c>
+      <c r="D21" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s">
+        <v>329</v>
+      </c>
+      <c r="C22" t="s">
+        <v>332</v>
+      </c>
+      <c r="D22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" t="s">
+        <v>329</v>
+      </c>
+      <c r="C23" t="s">
+        <v>333</v>
+      </c>
+      <c r="D23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>334</v>
+      </c>
+      <c r="B24" t="s">
+        <v>329</v>
+      </c>
+      <c r="C24" t="s">
+        <v>320</v>
+      </c>
+      <c r="D24" t="s">
+        <v>335</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2122232B-336C-48B5-9283-6A91D40EFFD9}">
   <dimension ref="A1:S58"/>
@@ -4153,13 +4682,13 @@
       <c r="C3" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="D3" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
       <c r="I3" s="13" t="s">
         <v>173</v>
       </c>
@@ -5486,11 +6015,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="41"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="42"/>
       <c r="E1" s="11"/>
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
@@ -5793,11 +6322,11 @@
       <c r="P23" s="11"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" s="42" t="s">
+      <c r="A24" s="43" t="s">
         <v>275</v>
       </c>
-      <c r="B24" s="43"/>
-      <c r="C24" s="44"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="45"/>
       <c r="D24" s="11"/>
       <c r="E24" s="20"/>
       <c r="H24" s="20"/>
@@ -5964,11 +6493,11 @@
     </row>
     <row r="43" spans="1:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="45" t="s">
+      <c r="A44" s="46" t="s">
         <v>276</v>
       </c>
-      <c r="B44" s="46"/>
-      <c r="C44" s="47"/>
+      <c r="B44" s="47"/>
+      <c r="C44" s="48"/>
     </row>
     <row r="45" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="33" t="s">
@@ -6098,11 +6627,11 @@
     </row>
     <row r="59" spans="1:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A60" s="48" t="s">
+      <c r="A60" s="49" t="s">
         <v>277</v>
       </c>
-      <c r="B60" s="49"/>
-      <c r="C60" s="50"/>
+      <c r="B60" s="50"/>
+      <c r="C60" s="51"/>
     </row>
     <row r="61" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="33" t="s">
